--- a/gallabox_api_flows.xlsx
+++ b/gallabox_api_flows.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="555" windowWidth="19815" windowHeight="7365"/>
+    <workbookView xWindow="390" yWindow="555" windowWidth="19815" windowHeight="7365" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="User Create Order Flow" sheetId="1" r:id="rId1"/>
@@ -619,7 +619,7 @@
     <col min="1" max="1" width="28.875" customWidth="1"/>
     <col min="2" max="2" width="55.875" customWidth="1"/>
     <col min="3" max="3" width="50.875" customWidth="1"/>
-    <col min="4" max="4" width="55.875" customWidth="1"/>
+    <col min="4" max="4" width="165.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.875" customWidth="1"/>
   </cols>
   <sheetData>
